--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28700" windowHeight="12800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28704" windowHeight="12804"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="324">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -1049,6 +1049,10 @@
   </si>
   <si>
     <t>1.新增业务明细信息登记模板</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1258,7 +1262,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1352,10 +1356,6 @@
     <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1704,23 +1704,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:AA2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" style="28" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.69921875" style="28" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="28" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.4140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
+    <col min="3" max="14" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="17" max="18" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
     <col min="19" max="19" width="18.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.4140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.4140625" style="28" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="18.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
     <col min="23" max="23" width="17.5" style="28" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="24" style="28" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="15.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.9140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.4140625" style="28" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="16.8984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.3984375" style="28" customWidth="1" collapsed="1"/>
     <col min="28" max="16384" width="9" style="29" collapsed="1"/>
   </cols>
   <sheetData>
@@ -1807,34 +1807,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="32" customFormat="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
+    <row r="2" spans="1:27">
+      <c r="R2" s="28" t="s">
+        <v>323</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1888,35 +1864,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="73.33203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1">
       <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="31">
+    <row r="2" spans="1:1" ht="31.8">
       <c r="A2" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.5">
+    <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.5">
+    <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5">
+    <row r="5" spans="1:1">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="15.5">
+    <row r="6" spans="1:1">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -3541,9 +3517,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
@@ -3563,7 +3539,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29.15" customHeight="1">
+    <row r="3" spans="1:2" ht="29.1" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>321</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -1049,10 +1049,6 @@
   </si>
   <si>
     <t>1.新增业务明细信息登记模板</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1262,7 +1258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1347,14 +1343,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1707,110 +1709,134 @@
   <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" style="28" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18" style="28" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="18.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.3984375" style="28" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="17.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="24" style="28" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="15.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.8984375" style="28" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.3984375" style="28" customWidth="1" collapsed="1"/>
-    <col min="28" max="16384" width="9" style="29" collapsed="1"/>
+    <col min="1" max="1" width="22.69921875" style="30" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18" style="30" customWidth="1" collapsed="1"/>
+    <col min="3" max="14" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="19.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="17" max="18" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="18.5" style="30" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="18.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="19.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="17.5" style="30" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="24" style="30" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="15.5" style="30" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="16.8984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="28" max="16384" width="9" style="28" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="L1" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="U1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="V1" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="30" t="s">
+      <c r="W1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="X1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="Y1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="Z1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AA1" s="29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
-      <c r="R2" s="28" t="s">
-        <v>323</v>
-      </c>
+    <row r="2" spans="1:27" s="32" customFormat="1">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
@@ -5,14 +5,14 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28704" windowHeight="12804"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28710" windowHeight="12810"/>
   </bookViews>
   <sheets>
-    <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
+    <sheet name="投资者明细信息登记" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
     <sheet name="版本号1.0.0" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -1707,22 +1707,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.69921875" style="30" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.75" style="30" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="30" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.3984375" style="30" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
+    <col min="3" max="14" width="26.125" style="30" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="19.375" style="30" customWidth="1" collapsed="1"/>
+    <col min="17" max="18" width="26.125" style="30" customWidth="1" collapsed="1"/>
     <col min="19" max="19" width="18.5" style="30" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.09765625" style="30" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.3984375" style="30" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.125" style="30" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="18.375" style="30" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="19.375" style="30" customWidth="1" collapsed="1"/>
     <col min="23" max="23" width="17.5" style="30" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="24" style="30" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="15.5" style="30" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.8984375" style="30" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.3984375" style="30" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="16.875" style="30" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.375" style="30" customWidth="1" collapsed="1"/>
     <col min="28" max="16384" width="9" style="28" collapsed="1"/>
   </cols>
   <sheetData>
@@ -1890,35 +1890,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="73.296875" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.25" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="31.8">
+    <row r="2" spans="1:1" ht="30">
       <c r="A2" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" ht="15.75">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -3543,9 +3543,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
